--- a/Project Outputs for UZ_A_MAX11331_Adapter/Rev03/BOM_JLC/BOM_JLC_UZ_A_MAX11331_Adapter_SMD_Assembly_Rev03.xlsx
+++ b/Project Outputs for UZ_A_MAX11331_Adapter/Rev03/BOM_JLC/BOM_JLC_UZ_A_MAX11331_Adapter_SMD_Assembly_Rev03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ga92wum\git\UltraZohm\PCB\UZ_A_MAX11331_Adapter\Project Outputs for UZ_A_MAX11331_Adapter\Rev03\BOM_JLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57258B79-AC02-4819-8B28-1FBDC00D616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0357C9B-94AD-44A6-855E-D60C81D6682D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CC3D5B7C-2FE5-49A1-81F1-DF4516AC1ECC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{87B16D35-A2D5-49BB-977D-5C5E329A1293}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_UZ_A_MAX11331_Adapter_S" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="145">
   <si>
     <t>Comment</t>
   </si>
@@ -302,12 +302,15 @@
     <t>SMD resistor E24 series</t>
   </si>
   <si>
-    <t>220</t>
+    <t>220R</t>
   </si>
   <si>
     <t>R30</t>
   </si>
   <si>
+    <t>C1226</t>
+  </si>
+  <si>
     <t>RC0603JR-07220RL</t>
   </si>
   <si>
@@ -468,6 +471,9 @@
   </si>
   <si>
     <t>2.54mm Double Row Terminal Assembly, Right-Angled</t>
+  </si>
+  <si>
+    <t>C4184</t>
   </si>
 </sst>
 </file>
@@ -863,7 +869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9111CC00-66D3-403E-B948-15230D4CE537}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC9D6656-FCB2-4193-891A-701942090182}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1281,32 +1287,36 @@
       <c r="C21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="1"/>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1314,16 +1324,16 @@
         <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>86</v>
@@ -1332,191 +1342,191 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
